--- a/data/operations.xlsx
+++ b/data/operations.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,6 +608,161 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2024-01-05</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1234567812345678</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Развлечения</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Кино</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2024-01-18</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>8765432187654321</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-75</v>
+      </c>
+      <c r="D8" t="n">
+        <v>75</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Кафе</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Кофе</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2024-01-22</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1234567812345678</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-500</v>
+      </c>
+      <c r="D9" t="n">
+        <v>500</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Одежда</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Покупка одежды</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2024-01-08</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>8765432187654321</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-2000</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Техника</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Телефон</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2024-01-28</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1234567812345678</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-80</v>
+      </c>
+      <c r="D11" t="n">
+        <v>80</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Косметика</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Косметика</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
